--- a/BVSimulationFiles/81.xlsx
+++ b/BVSimulationFiles/81.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.003273809523809524</v>
+        <v>0.006547619047619048</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003272109006445259</v>
+        <v>0.006544218012890518</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003270409372382019</v>
+        <v>0.006540818744764038</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00326871062116099</v>
+        <v>0.00653742124232198</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003267012752323596</v>
+        <v>0.006534025504647192</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003265315765411501</v>
+        <v>0.006530631530823002</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003263619659966603</v>
+        <v>0.006527239319933206</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003261924435531045</v>
+        <v>0.00652384887106209</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0032602300916472</v>
+        <v>0.0065204601832944</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003258536627857685</v>
+        <v>0.00651707325571537</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00325684404370535</v>
+        <v>0.0065136880874107</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003255152338733286</v>
+        <v>0.006510304677466572</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003253461512484816</v>
+        <v>0.006506923024969632</v>
       </c>
       <c r="O2" t="n">
-        <v>0.00325177156450351</v>
+        <v>0.00650354312900702</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003250082494333164</v>
+        <v>0.006500164988666328</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003248394301517818</v>
+        <v>0.006496788603035636</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003246706985601747</v>
+        <v>0.006493413971203494</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003245020546129464</v>
+        <v>0.006490041092258928</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003243334982645713</v>
+        <v>0.006486669965291426</v>
       </c>
       <c r="U2" t="n">
-        <v>0.003241650294695482</v>
+        <v>0.006483300589390964</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.003273809523809524</v>
+        <v>0.006547619047619048</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003272109006445259</v>
+        <v>0.006544218012890518</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003270409372382019</v>
+        <v>0.006540818744764038</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00326871062116099</v>
+        <v>0.00653742124232198</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003267012752323596</v>
+        <v>0.006534025504647192</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003265315765411501</v>
+        <v>0.006530631530823002</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003263619659966603</v>
+        <v>0.006527239319933206</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003261924435531045</v>
+        <v>0.00652384887106209</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0032602300916472</v>
+        <v>0.0065204601832944</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003258536627857685</v>
+        <v>0.00651707325571537</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00325684404370535</v>
+        <v>0.0065136880874107</v>
       </c>
       <c r="M3" t="n">
-        <v>0.003255152338733286</v>
+        <v>0.006510304677466572</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003253461512484816</v>
+        <v>0.006506923024969632</v>
       </c>
       <c r="O3" t="n">
-        <v>0.00325177156450351</v>
+        <v>0.00650354312900702</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003250082494333164</v>
+        <v>0.006500164988666328</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003248394301517818</v>
+        <v>0.006496788603035636</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003246706985601747</v>
+        <v>0.006493413971203494</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003245020546129464</v>
+        <v>0.006490041092258928</v>
       </c>
       <c r="T3" t="n">
-        <v>0.003243334982645713</v>
+        <v>0.006486669965291426</v>
       </c>
       <c r="U3" t="n">
-        <v>0.003241650294695482</v>
+        <v>0.006483300589390964</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/81.xlsx
+++ b/BVSimulationFiles/81.xlsx
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.006547619047619048</v>
+        <v>0.06547619047619048</v>
       </c>
       <c r="C2" t="n">
-        <v>0.006544218012890518</v>
+        <v>0.06544218012890518</v>
       </c>
       <c r="D2" t="n">
-        <v>0.006540818744764038</v>
+        <v>0.06540818744764038</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00653742124232198</v>
+        <v>0.06537421242321981</v>
       </c>
       <c r="F2" t="n">
-        <v>0.006534025504647192</v>
+        <v>0.06534025504647192</v>
       </c>
       <c r="G2" t="n">
-        <v>0.006530631530823002</v>
+        <v>0.06530631530823003</v>
       </c>
       <c r="H2" t="n">
-        <v>0.006527239319933206</v>
+        <v>0.06527239319933206</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00652384887106209</v>
+        <v>0.06523848871062091</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0065204601832944</v>
+        <v>0.06520460183294401</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00651707325571537</v>
+        <v>0.06517073255715369</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0065136880874107</v>
+        <v>0.065136880874107</v>
       </c>
       <c r="M2" t="n">
-        <v>0.006510304677466572</v>
+        <v>0.06510304677466572</v>
       </c>
       <c r="N2" t="n">
-        <v>0.006506923024969632</v>
+        <v>0.06506923024969632</v>
       </c>
       <c r="O2" t="n">
-        <v>0.00650354312900702</v>
+        <v>0.06503543129007019</v>
       </c>
       <c r="P2" t="n">
-        <v>0.006500164988666328</v>
+        <v>0.06500164988666328</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.006496788603035636</v>
+        <v>0.06496788603035636</v>
       </c>
       <c r="R2" t="n">
-        <v>0.006493413971203494</v>
+        <v>0.06493413971203495</v>
       </c>
       <c r="S2" t="n">
-        <v>0.006490041092258928</v>
+        <v>0.06490041092258927</v>
       </c>
       <c r="T2" t="n">
-        <v>0.006486669965291426</v>
+        <v>0.06486669965291426</v>
       </c>
       <c r="U2" t="n">
-        <v>0.006483300589390964</v>
+        <v>0.06483300589390964</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.006547619047619048</v>
+        <v>0.06547619047619048</v>
       </c>
       <c r="C3" t="n">
-        <v>0.006544218012890518</v>
+        <v>0.06544218012890518</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006540818744764038</v>
+        <v>0.06540818744764038</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00653742124232198</v>
+        <v>0.06537421242321981</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006534025504647192</v>
+        <v>0.06534025504647192</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006530631530823002</v>
+        <v>0.06530631530823003</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006527239319933206</v>
+        <v>0.06527239319933206</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00652384887106209</v>
+        <v>0.06523848871062091</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0065204601832944</v>
+        <v>0.06520460183294401</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00651707325571537</v>
+        <v>0.06517073255715369</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0065136880874107</v>
+        <v>0.065136880874107</v>
       </c>
       <c r="M3" t="n">
-        <v>0.006510304677466572</v>
+        <v>0.06510304677466572</v>
       </c>
       <c r="N3" t="n">
-        <v>0.006506923024969632</v>
+        <v>0.06506923024969632</v>
       </c>
       <c r="O3" t="n">
-        <v>0.00650354312900702</v>
+        <v>0.06503543129007019</v>
       </c>
       <c r="P3" t="n">
-        <v>0.006500164988666328</v>
+        <v>0.06500164988666328</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.006496788603035636</v>
+        <v>0.06496788603035636</v>
       </c>
       <c r="R3" t="n">
-        <v>0.006493413971203494</v>
+        <v>0.06493413971203495</v>
       </c>
       <c r="S3" t="n">
-        <v>0.006490041092258928</v>
+        <v>0.06490041092258927</v>
       </c>
       <c r="T3" t="n">
-        <v>0.006486669965291426</v>
+        <v>0.06486669965291426</v>
       </c>
       <c r="U3" t="n">
-        <v>0.006483300589390964</v>
+        <v>0.06483300589390964</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/81.xlsx
+++ b/BVSimulationFiles/81.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -421,60 +421,90 @@
         <v>0</v>
       </c>
       <c r="C1" t="n">
-        <v>0.004193157894736842</v>
+        <v>0.002747241379310345</v>
       </c>
       <c r="D1" t="n">
-        <v>0.008386315789473684</v>
+        <v>0.005494482758620689</v>
       </c>
       <c r="E1" t="n">
-        <v>0.01257947368421052</v>
+        <v>0.008241724137931034</v>
       </c>
       <c r="F1" t="n">
-        <v>0.01677263157894737</v>
+        <v>0.01098896551724138</v>
       </c>
       <c r="G1" t="n">
-        <v>0.02096578947368421</v>
+        <v>0.01373620689655172</v>
       </c>
       <c r="H1" t="n">
-        <v>0.02515894736842105</v>
+        <v>0.01648344827586207</v>
       </c>
       <c r="I1" t="n">
-        <v>0.02935210526315789</v>
+        <v>0.01923068965517241</v>
       </c>
       <c r="J1" t="n">
-        <v>0.03354526315789474</v>
+        <v>0.02197793103448276</v>
       </c>
       <c r="K1" t="n">
-        <v>0.03773842105263158</v>
+        <v>0.0247251724137931</v>
       </c>
       <c r="L1" t="n">
-        <v>0.04193157894736842</v>
+        <v>0.02747241379310345</v>
       </c>
       <c r="M1" t="n">
-        <v>0.04612473684210526</v>
+        <v>0.03021965517241379</v>
       </c>
       <c r="N1" t="n">
-        <v>0.0503178947368421</v>
+        <v>0.03296689655172413</v>
       </c>
       <c r="O1" t="n">
-        <v>0.05451105263157895</v>
+        <v>0.03571413793103448</v>
       </c>
       <c r="P1" t="n">
-        <v>0.05870421052631578</v>
+        <v>0.03846137931034482</v>
       </c>
       <c r="Q1" t="n">
-        <v>0.06289736842105263</v>
+        <v>0.04120862068965517</v>
       </c>
       <c r="R1" t="n">
-        <v>0.06709052631578948</v>
+        <v>0.04395586206896551</v>
       </c>
       <c r="S1" t="n">
-        <v>0.0712836842105263</v>
+        <v>0.04670310344827586</v>
       </c>
       <c r="T1" t="n">
-        <v>0.07547684210526316</v>
+        <v>0.0494503448275862</v>
       </c>
       <c r="U1" t="n">
+        <v>0.05219758620689655</v>
+      </c>
+      <c r="V1" t="n">
+        <v>0.0549448275862069</v>
+      </c>
+      <c r="W1" t="n">
+        <v>0.05769206896551723</v>
+      </c>
+      <c r="X1" t="n">
+        <v>0.06043931034482758</v>
+      </c>
+      <c r="Y1" t="n">
+        <v>0.06318655172413792</v>
+      </c>
+      <c r="Z1" t="n">
+        <v>0.06593379310344827</v>
+      </c>
+      <c r="AA1" t="n">
+        <v>0.06868103448275861</v>
+      </c>
+      <c r="AB1" t="n">
+        <v>0.07142827586206896</v>
+      </c>
+      <c r="AC1" t="n">
+        <v>0.0741755172413793</v>
+      </c>
+      <c r="AD1" t="n">
+        <v>0.07692275862068965</v>
+      </c>
+      <c r="AE1" t="n">
         <v>0.07966999999999999</v>
       </c>
     </row>
@@ -483,64 +513,94 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.06547619047619048</v>
+        <v>0.2067630827204801</v>
       </c>
       <c r="C2" t="n">
-        <v>0.06544218012890518</v>
+        <v>0.206622364203261</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06540818744764038</v>
+        <v>0.2064817414560452</v>
       </c>
       <c r="E2" t="n">
-        <v>0.06537421242321981</v>
+        <v>0.2063412144136536</v>
       </c>
       <c r="F2" t="n">
-        <v>0.06534025504647192</v>
+        <v>0.2062007830109514</v>
       </c>
       <c r="G2" t="n">
-        <v>0.06530631530823003</v>
+        <v>0.2060604471828485</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06527239319933206</v>
+        <v>0.2059202068642988</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06523848871062091</v>
+        <v>0.2057800619903004</v>
       </c>
       <c r="J2" t="n">
-        <v>0.06520460183294401</v>
+        <v>0.205640012495896</v>
       </c>
       <c r="K2" t="n">
-        <v>0.06517073255715369</v>
+        <v>0.2055000583161721</v>
       </c>
       <c r="L2" t="n">
-        <v>0.065136880874107</v>
+        <v>0.2053601993862598</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06510304677466572</v>
+        <v>0.2052204356413339</v>
       </c>
       <c r="N2" t="n">
-        <v>0.06506923024969632</v>
+        <v>0.2050807670166137</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06503543129007019</v>
+        <v>0.2049411934473623</v>
       </c>
       <c r="P2" t="n">
-        <v>0.06500164988666328</v>
+        <v>0.2048017148688872</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.06496788603035636</v>
+        <v>0.2046623312165394</v>
       </c>
       <c r="R2" t="n">
-        <v>0.06493413971203495</v>
+        <v>0.2045230424257144</v>
       </c>
       <c r="S2" t="n">
-        <v>0.06490041092258927</v>
+        <v>0.2043838484318516</v>
       </c>
       <c r="T2" t="n">
-        <v>0.06486669965291426</v>
+        <v>0.204244749170434</v>
       </c>
       <c r="U2" t="n">
-        <v>0.06483300589390964</v>
+        <v>0.2041057445769889</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.2039668345870871</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.2038280191363436</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.2036892981604172</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.2035506715950102</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.2034121393758689</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.203273701438783</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.2031353577195866</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.2029971081541567</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.2028589526784144</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.2027208912283242</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +608,94 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06547619047619048</v>
+        <v>0.2067630827204801</v>
       </c>
       <c r="C3" t="n">
-        <v>0.06544218012890518</v>
+        <v>0.206622364203261</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06540818744764038</v>
+        <v>0.2064817414560452</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06537421242321981</v>
+        <v>0.2063412144136536</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06534025504647192</v>
+        <v>0.2062007830109514</v>
       </c>
       <c r="G3" t="n">
-        <v>0.06530631530823003</v>
+        <v>0.2060604471828485</v>
       </c>
       <c r="H3" t="n">
-        <v>0.06527239319933206</v>
+        <v>0.2059202068642988</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06523848871062091</v>
+        <v>0.2057800619903004</v>
       </c>
       <c r="J3" t="n">
-        <v>0.06520460183294401</v>
+        <v>0.205640012495896</v>
       </c>
       <c r="K3" t="n">
-        <v>0.06517073255715369</v>
+        <v>0.2055000583161721</v>
       </c>
       <c r="L3" t="n">
-        <v>0.065136880874107</v>
+        <v>0.2053601993862598</v>
       </c>
       <c r="M3" t="n">
-        <v>0.06510304677466572</v>
+        <v>0.2052204356413339</v>
       </c>
       <c r="N3" t="n">
-        <v>0.06506923024969632</v>
+        <v>0.2050807670166137</v>
       </c>
       <c r="O3" t="n">
-        <v>0.06503543129007019</v>
+        <v>0.2049411934473623</v>
       </c>
       <c r="P3" t="n">
-        <v>0.06500164988666328</v>
+        <v>0.2048017148688872</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.06496788603035636</v>
+        <v>0.2046623312165394</v>
       </c>
       <c r="R3" t="n">
-        <v>0.06493413971203495</v>
+        <v>0.2045230424257144</v>
       </c>
       <c r="S3" t="n">
-        <v>0.06490041092258927</v>
+        <v>0.2043838484318516</v>
       </c>
       <c r="T3" t="n">
-        <v>0.06486669965291426</v>
+        <v>0.204244749170434</v>
       </c>
       <c r="U3" t="n">
-        <v>0.06483300589390964</v>
+        <v>0.2041057445769889</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.2039668345870871</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.2038280191363436</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.2036892981604172</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.2035506715950102</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.2034121393758689</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.203273701438783</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.2031353577195866</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.2029971081541567</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.2028589526784144</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.2027208912283242</v>
       </c>
     </row>
   </sheetData>
